--- a/02_Inputs/SEA AI Avatars.xlsx
+++ b/02_Inputs/SEA AI Avatars.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ben/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ben/Documents/UNDP/SEH/Sustainable Energy Academy/CMS/02_Inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3350438E-F3CB-AB49-A5CE-74450786B97D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFF8A210-30A4-7D48-8EDA-AEBE121CD742}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3960" yWindow="4360" windowWidth="24440" windowHeight="12760" xr2:uid="{9EE7F737-BF97-BD45-87C0-2E9E7D5ABBFE}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="47">
   <si>
     <t>Lesson</t>
   </si>
@@ -80,7 +80,7 @@
     <t>Onat</t>
   </si>
   <si>
-    <t>Onat - Professional</t>
+    <t>Professional</t>
   </si>
   <si>
     <t>es</t>
@@ -92,9 +92,6 @@
     <t>Shirley</t>
   </si>
   <si>
-    <t>Shirley - Professional</t>
-  </si>
-  <si>
     <t>Spanish (Colombia)</t>
   </si>
   <si>
@@ -116,19 +113,99 @@
     <t>Armando</t>
   </si>
   <si>
-    <t>Armando - Professional</t>
-  </si>
-  <si>
     <t>1.0.0</t>
+  </si>
+  <si>
+    <t>Salma</t>
+  </si>
+  <si>
+    <t>Relaxed Rachel</t>
+  </si>
+  <si>
+    <t>Jason</t>
+  </si>
+  <si>
+    <t>Broadcaster</t>
+  </si>
+  <si>
+    <t>Spanish (Costa Rica)</t>
+  </si>
+  <si>
+    <t>Vivianna</t>
+  </si>
+  <si>
+    <t>Grace Parker</t>
+  </si>
+  <si>
+    <t>Judy</t>
+  </si>
+  <si>
+    <t>Portuguese (Brazil)</t>
+  </si>
+  <si>
+    <t>1.1.0</t>
+  </si>
+  <si>
+    <t>Carla</t>
+  </si>
+  <si>
+    <t>Claire - Excited</t>
+  </si>
+  <si>
+    <t>English (Nigeria)</t>
+  </si>
+  <si>
+    <t>Matthew</t>
+  </si>
+  <si>
+    <t>Instructor Ishaan</t>
+  </si>
+  <si>
+    <t>Gabriel</t>
+  </si>
+  <si>
+    <t>Caroline</t>
+  </si>
+  <si>
+    <t>Caroline Public</t>
+  </si>
+  <si>
+    <t>Shawn</t>
+  </si>
+  <si>
+    <t>1.1.1</t>
+  </si>
+  <si>
+    <t>Bahar</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+    </font>
+    <font>
+      <sz val="14"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -155,8 +232,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -491,7 +571,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B67CD3F-C423-F04C-B440-CC71BD178B55}">
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.83203125" customWidth="1"/>
@@ -499,31 +579,31 @@
     <col min="5" max="5" width="22.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+    <row r="1" spans="1:6" s="3" customFormat="1" ht="19" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
+      <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C2" t="s">
@@ -540,10 +620,10 @@
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
+      <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C3" t="s">
@@ -560,10 +640,10 @@
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
+      <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C4" t="s">
@@ -573,89 +653,349 @@
         <v>17</v>
       </c>
       <c r="E4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" t="s">
         <v>18</v>
       </c>
-      <c r="F4" t="s">
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>19</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" t="s">
-        <v>20</v>
       </c>
       <c r="C5" t="s">
         <v>8</v>
       </c>
       <c r="D5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" t="s">
         <v>21</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>22</v>
       </c>
-      <c r="F5" t="s">
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>23</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" t="s">
-        <v>24</v>
       </c>
       <c r="C6" t="s">
         <v>8</v>
       </c>
       <c r="D6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E6" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="F6" t="s">
         <v>11</v>
       </c>
     </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" t="s">
+        <v>11</v>
+      </c>
+    </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
+      <c r="A8" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" t="s">
+        <v>16</v>
+      </c>
+      <c r="D8" t="s">
+        <v>26</v>
+      </c>
+      <c r="E8" t="s">
         <v>27</v>
-      </c>
-      <c r="B8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" t="s">
-        <v>8</v>
-      </c>
-      <c r="D8" t="s">
-        <v>9</v>
-      </c>
-      <c r="E8" t="s">
-        <v>10</v>
       </c>
       <c r="F8" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>27</v>
-      </c>
-      <c r="B9" t="s">
-        <v>12</v>
+      <c r="A9" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>15</v>
       </c>
       <c r="C9" t="s">
         <v>8</v>
       </c>
       <c r="D9" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="E9" t="s">
+        <v>29</v>
+      </c>
+      <c r="F9" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A10" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" t="s">
+        <v>16</v>
+      </c>
+      <c r="D10" t="s">
+        <v>31</v>
+      </c>
+      <c r="E10" t="s">
+        <v>32</v>
+      </c>
+      <c r="F10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A11" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D11" t="s">
+        <v>33</v>
+      </c>
+      <c r="E11" t="s">
         <v>14</v>
       </c>
-      <c r="F9" t="s">
+      <c r="F11" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A12" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" t="s">
+        <v>16</v>
+      </c>
+      <c r="D12" t="s">
+        <v>36</v>
+      </c>
+      <c r="E12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F12" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A13" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C13" t="s">
+        <v>8</v>
+      </c>
+      <c r="D13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E13" t="s">
+        <v>40</v>
+      </c>
+      <c r="F13" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A14" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C14" t="s">
+        <v>8</v>
+      </c>
+      <c r="D14" t="s">
+        <v>41</v>
+      </c>
+      <c r="E14" t="s">
+        <v>40</v>
+      </c>
+      <c r="F14" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A15" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C15" t="s">
+        <v>16</v>
+      </c>
+      <c r="D15" t="s">
+        <v>42</v>
+      </c>
+      <c r="E15" t="s">
+        <v>43</v>
+      </c>
+      <c r="F15" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A16" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C16" t="s">
+        <v>8</v>
+      </c>
+      <c r="D16" t="s">
+        <v>44</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F16" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A17" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" t="s">
+        <v>16</v>
+      </c>
+      <c r="D17" t="s">
+        <v>36</v>
+      </c>
+      <c r="E17" t="s">
+        <v>37</v>
+      </c>
+      <c r="F17" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A18" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C18" t="s">
+        <v>16</v>
+      </c>
+      <c r="D18" t="s">
+        <v>46</v>
+      </c>
+      <c r="E18" t="s">
+        <v>14</v>
+      </c>
+      <c r="F18" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A19" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C19" t="s">
+        <v>16</v>
+      </c>
+      <c r="D19" t="s">
+        <v>17</v>
+      </c>
+      <c r="E19" t="s">
+        <v>14</v>
+      </c>
+      <c r="F19" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A20" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C20" t="s">
+        <v>8</v>
+      </c>
+      <c r="D20" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" t="s">
+        <v>21</v>
+      </c>
+      <c r="F20" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A21" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C21" t="s">
+        <v>8</v>
+      </c>
+      <c r="D21" t="s">
+        <v>24</v>
+      </c>
+      <c r="E21" t="s">
+        <v>14</v>
+      </c>
+      <c r="F21" t="s">
         <v>11</v>
       </c>
     </row>
@@ -665,17 +1005,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="c8670835-afc4-4376-8ae0-1ffed5b27e6b" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b0bf4113-6f4a-4f3e-b5bb-503c4d9102e3">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -684,7 +1013,7 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010098970033F315F542A2D9640B7CC02236" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="94449e8ff35cec47b43afd2e381d9e90">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b0bf4113-6f4a-4f3e-b5bb-503c4d9102e3" xmlns:ns3="c8670835-afc4-4376-8ae0-1ffed5b27e6b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="f7f21ad7dc1dad656b5a5a7699096a32" ns2:_="" ns3:_="">
     <xsd:import namespace="b0bf4113-6f4a-4f3e-b5bb-503c4d9102e3"/>
@@ -925,18 +1254,18 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5DBDB08E-AB1C-4A50-B848-63D5C5AD2E74}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="c8670835-afc4-4376-8ae0-1ffed5b27e6b"/>
-    <ds:schemaRef ds:uri="b0bf4113-6f4a-4f3e-b5bb-503c4d9102e3"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="c8670835-afc4-4376-8ae0-1ffed5b27e6b" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b0bf4113-6f4a-4f3e-b5bb-503c4d9102e3">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{11E68986-1150-4E56-A876-ACDFC93A867C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
@@ -944,7 +1273,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FC7A272E-D4A4-4CB1-AFE6-69FD613CEF01}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -961,4 +1290,15 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5DBDB08E-AB1C-4A50-B848-63D5C5AD2E74}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="c8670835-afc4-4376-8ae0-1ffed5b27e6b"/>
+    <ds:schemaRef ds:uri="b0bf4113-6f4a-4f3e-b5bb-503c4d9102e3"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>